--- a/samples/示例登分表_九年级.xlsx
+++ b/samples/示例登分表_九年级.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>王一远</t>
+          <t>王疏野</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>朱墨言</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>刘佳轩</t>
+          <t>刘听禾</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>赵子桐</t>
+          <t>赵砚乔</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>刘明轩</t>
+          <t>刘和禾</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>赵雨宇</t>
+          <t>赵南白</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>高明怡</t>
+          <t>高和言</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>何子诺</t>
+          <t>何砚桐</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>赵雨轩</t>
+          <t>赵南禾</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>徐浩琪</t>
+          <t>徐书澜</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>黄明宇</t>
+          <t>黄和白</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杨佳涵</t>
+          <t>杨听秋</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>赵雨琪</t>
+          <t>赵南澜</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>刘浩桐</t>
+          <t>刘书乔</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>罗俊诺</t>
+          <t>罗北桐</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>王梓怡</t>
+          <t>王青言</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>王明轩</t>
+          <t>王和舟</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>吴浩轩</t>
+          <t>吴书禾</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>孙梓杰</t>
+          <t>孙青辰</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>朱雨轩</t>
+          <t>朱南舟</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>王浩诺</t>
+          <t>王书桐</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>孙梓杰</t>
+          <t>孙青辰</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>王俊远</t>
+          <t>王北野</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>罗子宇</t>
+          <t>罗砚白</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>陈佳涵</t>
+          <t>陈听秋</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>刘子诺</t>
+          <t>刘砚桐</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>吴俊杰</t>
+          <t>吴北辰</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>赵梓诺</t>
+          <t>赵青桐</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>马梓远</t>
+          <t>马青野</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>何浩杰</t>
+          <t>何书辰</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杨浩远</t>
+          <t>杨书野</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>孙佳轩</t>
+          <t>孙听禾</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>王佳杰</t>
+          <t>王听辰</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>黄欣诺</t>
+          <t>黄墨桐</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>刘俊怡</t>
+          <t>刘北言</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>高子诺</t>
+          <t>高砚桐</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杨明宇</t>
+          <t>杨和白</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>徐梓怡</t>
+          <t>徐青言</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>马子宇</t>
+          <t>马砚白</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>赵思轩</t>
+          <t>赵星舟</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>朱俊怡</t>
+          <t>朱北言</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>孙思涵</t>
+          <t>孙星秋</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>刘佳琪</t>
+          <t>刘听澜</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>杨思涵</t>
+          <t>杨星秋</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>张浩桐</t>
+          <t>张书乔</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>孙思远</t>
+          <t>孙星野</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>刘子诺</t>
+          <t>刘砚桐</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>杨浩宇</t>
+          <t>杨书白</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>郭欣轩</t>
+          <t>郭墨舟</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>周欣宇</t>
+          <t>周墨白</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>郭思诺</t>
+          <t>郭星桐</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>徐浩杰</t>
+          <t>徐书辰</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>何子琪</t>
+          <t>何砚澜</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>徐思杰</t>
+          <t>徐星辰</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>徐俊宇</t>
+          <t>徐北白</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>郭浩琪</t>
+          <t>郭书澜</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>林浩宇</t>
+          <t>林书白</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>张佳宇</t>
+          <t>张听白</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>赵俊轩</t>
+          <t>赵北舟</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>杨子轩</t>
+          <t>杨砚舟</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>陈梓诺</t>
+          <t>陈青桐</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>黄俊远</t>
+          <t>黄北野</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>周明怡</t>
+          <t>周和言</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>马欣桐</t>
+          <t>马墨乔</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>郭思琪</t>
+          <t>郭星澜</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>高欣远</t>
+          <t>高墨野</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>赵子桐</t>
+          <t>赵砚乔</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>吴思宇</t>
+          <t>吴星白</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>杨明琪</t>
+          <t>杨和澜</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>张欣诺</t>
+          <t>张墨桐</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>孙浩怡</t>
+          <t>孙书言</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>郭梓轩</t>
+          <t>郭青禾</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>杨一杰</t>
+          <t>杨疏辰</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>周俊桐</t>
+          <t>周北乔</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>赵浩涵</t>
+          <t>赵书秋</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>罗子诺</t>
+          <t>罗砚桐</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>马子轩</t>
+          <t>马砚禾</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>郭欣桐</t>
+          <t>郭墨乔</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>朱一杰</t>
+          <t>朱疏辰</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>郭梓诺</t>
+          <t>郭青桐</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>吴俊轩</t>
+          <t>吴北舟</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>李俊诺</t>
+          <t>李北桐</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>孙子怡</t>
+          <t>孙砚言</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>马梓涵</t>
+          <t>马青秋</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>孙一琪</t>
+          <t>孙疏澜</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>吴梓远</t>
+          <t>吴青野</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>马梓怡</t>
+          <t>马青言</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>罗子宇</t>
+          <t>罗砚白</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>马明轩</t>
+          <t>马和禾</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>赵俊宇</t>
+          <t>赵北白</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>周一远</t>
+          <t>周疏野</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>刘浩轩</t>
+          <t>刘书舟</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>林子轩</t>
+          <t>林砚禾</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>刘一诺</t>
+          <t>刘疏桐</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>张佳杰</t>
+          <t>张听辰</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>赵思宇</t>
+          <t>赵星白</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>陈浩涵</t>
+          <t>陈书秋</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>孙佳远</t>
+          <t>孙听野</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>李浩怡</t>
+          <t>李书言</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>王思桐</t>
+          <t>王星乔</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>何浩轩</t>
+          <t>何书禾</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>吴浩桐</t>
+          <t>吴书乔</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>马梓诺</t>
+          <t>马青桐</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>孙雨远</t>
+          <t>孙南野</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>杨俊琪</t>
+          <t>杨北澜</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>何子桐</t>
+          <t>何砚乔</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>黄明轩</t>
+          <t>黄和舟</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>马俊轩</t>
+          <t>马北舟</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>何俊怡</t>
+          <t>何北言</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>高一涵</t>
+          <t>高疏秋</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>刘俊远</t>
+          <t>刘北野</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>高俊宇</t>
+          <t>高北白</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>何梓琪</t>
+          <t>何青澜</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>张雨怡</t>
+          <t>张南言</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>马雨宇</t>
+          <t>马南白</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>马明轩</t>
+          <t>马和禾</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>吴雨远</t>
+          <t>吴南野</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>林明涵</t>
+          <t>林和秋</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>朱俊轩</t>
+          <t>朱北禾</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>高子琪</t>
+          <t>高砚澜</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>李佳涵</t>
+          <t>李听秋</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>黄欣宇</t>
+          <t>黄墨白</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>孙一轩</t>
+          <t>孙疏禾</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>马佳怡</t>
+          <t>马听言</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>胡佳杰</t>
+          <t>胡听辰</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>黄俊琪</t>
+          <t>黄北澜</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>郭子怡</t>
+          <t>郭砚言</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>郭雨杰</t>
+          <t>郭南辰</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>孙俊宇</t>
+          <t>孙北白</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>张梓怡</t>
+          <t>张青言</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>张一怡</t>
+          <t>张疏言</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>徐明涵</t>
+          <t>徐和秋</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>朱子怡</t>
+          <t>朱砚言</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>周子远</t>
+          <t>周砚野</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>张思涵</t>
+          <t>张星秋</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>孙俊诺</t>
+          <t>孙北桐</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>张俊宇</t>
+          <t>张北白</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>郭浩轩</t>
+          <t>郭书禾</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>张佳涵</t>
+          <t>张听秋</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>何一涵</t>
+          <t>何疏秋</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>杨佳远</t>
+          <t>杨听野</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>吴俊远</t>
+          <t>吴北野</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>何子轩</t>
+          <t>何砚禾</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>王浩宇</t>
+          <t>王书白</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>周欣轩</t>
+          <t>周墨禾</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>何雨涵</t>
+          <t>何南秋</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>赵俊怡</t>
+          <t>赵北言</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>王思轩</t>
+          <t>王星禾</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>胡子桐</t>
+          <t>胡砚乔</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>何俊桐</t>
+          <t>何北乔</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>马俊杰</t>
+          <t>马北辰</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>黄佳怡</t>
+          <t>黄听言</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>罗子涵</t>
+          <t>罗砚秋</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>胡浩桐</t>
+          <t>胡书乔</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>徐浩琪</t>
+          <t>徐书澜</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>孙佳轩</t>
+          <t>孙听舟</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>黄子诺</t>
+          <t>黄砚桐</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>胡明杰</t>
+          <t>胡和辰</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>赵思杰</t>
+          <t>赵星辰</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>李梓涵</t>
+          <t>李青秋</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>高思涵</t>
+          <t>高星秋</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>徐子桐</t>
+          <t>徐砚乔</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>李欣涵</t>
+          <t>李墨秋</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>周思桐</t>
+          <t>周星乔</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>李俊杰</t>
+          <t>李北辰</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>胡雨涵</t>
+          <t>胡南秋</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>郭俊琪</t>
+          <t>郭北澜</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>高子怡</t>
+          <t>高砚言</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>郭梓远</t>
+          <t>郭青野</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>罗浩涵</t>
+          <t>罗书秋</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>黄浩琪</t>
+          <t>黄书澜</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>王思宇</t>
+          <t>王星白</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>杨梓远</t>
+          <t>杨青野</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>郭雨涵</t>
+          <t>郭南秋</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>胡佳杰</t>
+          <t>胡听辰</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>赵一诺</t>
+          <t>赵疏桐</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>林明怡</t>
+          <t>林和言</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>罗浩杰</t>
+          <t>罗书辰</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>马明琪</t>
+          <t>马和澜</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>林俊远</t>
+          <t>林北野</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>刘明轩</t>
+          <t>刘和舟</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>杨子远</t>
+          <t>杨砚野</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>周明轩</t>
+          <t>周和禾</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>王子远</t>
+          <t>王砚野</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>罗雨轩</t>
+          <t>罗南禾</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>胡明琪</t>
+          <t>胡和澜</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>罗思远</t>
+          <t>罗星野</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>张梓怡</t>
+          <t>张青言</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>吴浩琪</t>
+          <t>吴书澜</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>周佳远</t>
+          <t>周听野</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>朱雨诺</t>
+          <t>朱南桐</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>杨佳轩</t>
+          <t>杨听禾</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>张浩涵</t>
+          <t>张书秋</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>罗明轩</t>
+          <t>罗和舟</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>何俊远</t>
+          <t>何北野</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>马一怡</t>
+          <t>马疏言</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>高浩杰</t>
+          <t>高书辰</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>朱俊怡</t>
+          <t>朱北言</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>罗思宇</t>
+          <t>罗星白</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>马子怡</t>
+          <t>马砚言</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>李俊诺</t>
+          <t>李北桐</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>马佳怡</t>
+          <t>马听言</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>马俊杰</t>
+          <t>马北辰</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>赵梓琪</t>
+          <t>赵青澜</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>张欣宇</t>
+          <t>张墨白</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>杨佳琪</t>
+          <t>杨听澜</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>马佳宇</t>
+          <t>马听白</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>高梓宇</t>
+          <t>高青白</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>高欣杰</t>
+          <t>高墨辰</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>陈欣诺</t>
+          <t>陈墨桐</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>马雨宇</t>
+          <t>马南白</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>高俊杰</t>
+          <t>高北辰</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>高明远</t>
+          <t>高和野</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>李明远</t>
+          <t>李和野</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>高子杰</t>
+          <t>高砚辰</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>张梓轩</t>
+          <t>张青舟</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>杨浩诺</t>
+          <t>杨书桐</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>王雨轩</t>
+          <t>王南舟</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>胡欣宇</t>
+          <t>胡墨白</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>黄俊宇</t>
+          <t>黄北白</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>罗雨怡</t>
+          <t>罗南言</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>王浩涵</t>
+          <t>王书秋</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>吴明怡</t>
+          <t>吴和言</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>孙明诺</t>
+          <t>孙和桐</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>王佳琪</t>
+          <t>王听澜</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>胡佳诺</t>
+          <t>胡听桐</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>周佳远</t>
+          <t>周听野</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>朱梓宇</t>
+          <t>朱青白</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>徐思远</t>
+          <t>徐星野</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>朱思琪</t>
+          <t>朱星澜</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>高欣轩</t>
+          <t>高墨舟</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>徐子怡</t>
+          <t>徐砚言</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>罗佳远</t>
+          <t>罗听野</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>陈欣诺</t>
+          <t>陈墨桐</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>孙雨轩</t>
+          <t>孙南禾</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>陈俊轩</t>
+          <t>陈北禾</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>高子琪</t>
+          <t>高砚澜</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>高雨诺</t>
+          <t>高南桐</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>张俊桐</t>
+          <t>张北乔</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>赵梓怡</t>
+          <t>赵青言</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>周俊轩</t>
+          <t>周北舟</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -10372,7 +10372,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>林思杰</t>
+          <t>林星辰</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>陈雨宇</t>
+          <t>陈南白</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>郭浩怡</t>
+          <t>郭书言</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>徐欣轩</t>
+          <t>徐墨舟</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>吴佳远</t>
+          <t>吴听野</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>刘梓诺</t>
+          <t>刘青桐</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>孙雨诺</t>
+          <t>孙南桐</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>罗明琪</t>
+          <t>罗和澜</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>郭俊远</t>
+          <t>郭北野</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>周明轩</t>
+          <t>周和禾</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>吴子桐</t>
+          <t>吴砚乔</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>林佳怡</t>
+          <t>林听言</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>胡佳怡</t>
+          <t>胡听言</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>刘明远</t>
+          <t>刘和野</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>王梓杰</t>
+          <t>王青辰</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>马佳轩</t>
+          <t>马听禾</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>胡浩桐</t>
+          <t>胡书乔</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>李佳桐</t>
+          <t>李听乔</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>高浩杰</t>
+          <t>高书辰</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>陈明轩</t>
+          <t>陈和舟</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>林欣桐</t>
+          <t>林墨乔</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>周明诺</t>
+          <t>周和桐</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>吴俊桐</t>
+          <t>吴北乔</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>周一怡</t>
+          <t>周疏言</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>刘梓宇</t>
+          <t>刘青白</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>徐明杰</t>
+          <t>徐和辰</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>吴雨杰</t>
+          <t>吴南辰</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>陈欣桐</t>
+          <t>陈墨乔</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>朱一轩</t>
+          <t>朱疏舟</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
